--- a/provider_specialty_cprd_V.0.4_omop2.xlsx
+++ b/provider_specialty_cprd_V.0.4_omop2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/OMOP_Validation study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{C1ED8615-1082-41F3-85F1-DD4D8090F76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF604656-AD58-4174-BE6F-0BB18B80BE9E}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{C1ED8615-1082-41F3-85F1-DD4D8090F76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56E7D9AA-FC69-48AF-AF11-E92450919D72}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46870897-BCFD-414C-A471-BD3159C3E0A3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{46870897-BCFD-414C-A471-BD3159C3E0A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -455,17 +455,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -817,19 +807,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01908DF-AC8E-4A47-8381-A0A0F45C789A}">
   <dimension ref="A1:I63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +848,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>38003638</v>
       </c>
@@ -887,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>38003781</v>
       </c>
@@ -907,7 +897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>38003781</v>
       </c>
@@ -927,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>38004390</v>
       </c>
@@ -956,7 +946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>38004376</v>
       </c>
@@ -985,7 +975,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>38003789</v>
       </c>
@@ -1014,7 +1004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>38003789</v>
       </c>
@@ -1034,7 +1024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>38004413</v>
       </c>
@@ -1063,7 +1053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>38004446</v>
       </c>
@@ -1092,7 +1082,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>38004446</v>
       </c>
@@ -1121,7 +1111,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>38004169</v>
       </c>
@@ -1141,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>38004169</v>
       </c>
@@ -1161,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>38003659</v>
       </c>
@@ -1190,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>38004370</v>
       </c>
@@ -1219,7 +1209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>38003625</v>
       </c>
@@ -1239,7 +1229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>38003648</v>
       </c>
@@ -1259,7 +1249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>38003807</v>
       </c>
@@ -1288,7 +1278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0</v>
       </c>
@@ -1317,7 +1307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0</v>
       </c>
@@ -1346,7 +1336,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0</v>
       </c>
@@ -1375,7 +1365,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0</v>
       </c>
@@ -1404,7 +1394,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>38004487</v>
       </c>
@@ -1433,7 +1423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>38004185</v>
       </c>
@@ -1453,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>38004185</v>
       </c>
@@ -1473,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>38004185</v>
       </c>
@@ -1493,7 +1483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>38004185</v>
       </c>
@@ -1513,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>38004185</v>
       </c>
@@ -1533,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>38004185</v>
       </c>
@@ -1553,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>38003696</v>
       </c>
@@ -1582,7 +1572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>38003696</v>
       </c>
@@ -1611,7 +1601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>38003810</v>
       </c>
@@ -1631,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>38003819</v>
       </c>
@@ -1651,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>38003819</v>
       </c>
@@ -1680,7 +1670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>38004145</v>
       </c>
@@ -1700,7 +1690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>38004056</v>
       </c>
@@ -1729,7 +1719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>38004512</v>
       </c>
@@ -1749,7 +1739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>38004512</v>
       </c>
@@ -1769,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38004512</v>
       </c>
@@ -1798,7 +1788,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38004512</v>
       </c>
@@ -1818,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>38004153</v>
       </c>
@@ -1838,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>38004030</v>
       </c>
@@ -1867,7 +1857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>38003627</v>
       </c>
@@ -1896,7 +1886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>38004176</v>
       </c>
@@ -1916,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>38003722</v>
       </c>
@@ -1945,7 +1935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>38003690</v>
       </c>
@@ -1974,7 +1964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>38003731</v>
       </c>
@@ -1994,7 +1984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>38003731</v>
       </c>
@@ -2023,7 +2013,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>38003731</v>
       </c>
@@ -2052,7 +2042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>38003716</v>
       </c>
@@ -2081,7 +2071,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>38003716</v>
       </c>
@@ -2110,7 +2100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>38004154</v>
       </c>
@@ -2130,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>38004154</v>
       </c>
@@ -2150,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>38004154</v>
       </c>
@@ -2170,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>38004154</v>
       </c>
@@ -2190,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>38004154</v>
       </c>
@@ -2210,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>38003760</v>
       </c>
@@ -2239,7 +2229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>38004499</v>
       </c>
@@ -2268,7 +2258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>38003794</v>
       </c>
@@ -2297,7 +2287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>38003794</v>
       </c>
@@ -2326,7 +2316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>38003794</v>
       </c>
@@ -2355,7 +2345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>38004445</v>
       </c>
@@ -2375,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>38004371</v>
       </c>
@@ -2401,11 +2391,11 @@
       <sortCondition ref="B1:B63"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
